--- a/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/Ithaca Bakery_Triphammer_20260306.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/Ithaca Bakery_Triphammer_20260306.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1369,6 +1369,61 @@
         <v>83.29000000000001</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Smith Quality Eggs LLC</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Eggs (In-Shell)</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Flour - Millers Choice</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Mustard - Honey</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/Ithaca Bakery_Triphammer_20260306.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Ithaca Bakery/Ithaca Bakery_Triphammer_20260306.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1424,6 +1424,44 @@
         <v>0</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Copy Paper (8.5" x 11")</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Container - Plastic Hinged Pie (6")</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>54.99</v>
+      </c>
+      <c r="E52" t="n">
+        <v>54.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
